--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487692_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487692_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.3045</v>
+        <v>5.7232</v>
       </c>
       <c r="E2" t="n">
-        <v>1.9683</v>
+        <v>2.4688</v>
       </c>
       <c r="F2" t="n">
-        <v>3.3362</v>
+        <v>3.2544</v>
       </c>
       <c r="G2" t="n">
         <v>6.5621</v>
@@ -610,13 +610,13 @@
         <v>1.5523</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.4919</v>
+        <v>-0.0732</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.7145</v>
+        <v>-0.214</v>
       </c>
       <c r="U2" t="n">
-        <v>0.2226</v>
+        <v>0.1408</v>
       </c>
       <c r="V2" t="n">
         <v>-0.3776</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.4606</v>
+        <v>2.9963</v>
       </c>
       <c r="E3" t="n">
-        <v>2.5071</v>
+        <v>1.9065</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9535</v>
+        <v>1.0898</v>
       </c>
       <c r="G3" t="n">
         <v>2.9172</v>
@@ -688,13 +688,13 @@
         <v>0.3881</v>
       </c>
       <c r="S3" t="n">
-        <v>0.8434</v>
+        <v>0.3791</v>
       </c>
       <c r="T3" t="n">
-        <v>0.9836</v>
+        <v>0.383</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.1402</v>
+        <v>-0.0039</v>
       </c>
       <c r="V3" t="n">
         <v>0.2821</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A. FERNÁNDEZ GÓMEZ</t>
+          <t>D. VAZQUEZ JEREZ</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.9416</v>
+        <v>2.8468</v>
       </c>
       <c r="E4" t="n">
-        <v>2.9974</v>
+        <v>0.2354</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.0559</v>
+        <v>2.6113</v>
       </c>
       <c r="G4" t="n">
-        <v>4.7496</v>
+        <v>2.7794</v>
       </c>
       <c r="H4" t="n">
-        <v>-2.8481</v>
+        <v>1.4681</v>
       </c>
       <c r="I4" t="n">
-        <v>7.5977</v>
+        <v>1.3113</v>
       </c>
       <c r="J4" t="n">
-        <v>4.3973</v>
+        <v>1.2734</v>
       </c>
       <c r="K4" t="n">
-        <v>-2.5498</v>
+        <v>1.0298</v>
       </c>
       <c r="L4" t="n">
-        <v>6.9471</v>
+        <v>0.2436</v>
       </c>
       <c r="M4" t="n">
-        <v>0.3523</v>
+        <v>1.506</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.2983</v>
+        <v>0.4383</v>
       </c>
       <c r="O4" t="n">
-        <v>0.6506</v>
+        <v>1.0677</v>
       </c>
       <c r="P4" t="n">
-        <v>-5.2389</v>
+        <v>0.9702</v>
       </c>
       <c r="Q4" t="n">
-        <v>-6.9852</v>
+        <v>-0.194</v>
       </c>
       <c r="R4" t="n">
-        <v>1.7463</v>
+        <v>1.1642</v>
       </c>
       <c r="S4" t="n">
-        <v>0.0891</v>
+        <v>-0.2431</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.2042</v>
+        <v>-0.1842</v>
       </c>
       <c r="U4" t="n">
-        <v>0.2932</v>
+        <v>-0.0589</v>
       </c>
       <c r="V4" t="n">
-        <v>3.3418</v>
+        <v>-0.6597</v>
       </c>
       <c r="W4" t="n">
-        <v>5.7895</v>
+        <v>-0.6597</v>
       </c>
       <c r="X4" t="n">
-        <v>-2.4477</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>D. VAZQUEZ JEREZ</t>
+          <t>A. FERNÁNDEZ GÓMEZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.4042</v>
+        <v>2.5755</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.1254</v>
+        <v>3.2582</v>
       </c>
       <c r="F5" t="n">
-        <v>2.5296</v>
+        <v>-0.6827</v>
       </c>
       <c r="G5" t="n">
-        <v>2.7794</v>
+        <v>4.7496</v>
       </c>
       <c r="H5" t="n">
-        <v>1.4681</v>
+        <v>-2.8481</v>
       </c>
       <c r="I5" t="n">
-        <v>1.3113</v>
+        <v>7.5977</v>
       </c>
       <c r="J5" t="n">
-        <v>1.2734</v>
+        <v>4.3973</v>
       </c>
       <c r="K5" t="n">
-        <v>1.0298</v>
+        <v>-2.5498</v>
       </c>
       <c r="L5" t="n">
-        <v>0.2436</v>
+        <v>6.9471</v>
       </c>
       <c r="M5" t="n">
-        <v>1.506</v>
+        <v>0.3523</v>
       </c>
       <c r="N5" t="n">
-        <v>0.4383</v>
+        <v>-0.2983</v>
       </c>
       <c r="O5" t="n">
-        <v>1.0677</v>
+        <v>0.6506</v>
       </c>
       <c r="P5" t="n">
-        <v>0.9702</v>
+        <v>-5.2389</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.194</v>
+        <v>-6.9852</v>
       </c>
       <c r="R5" t="n">
-        <v>1.1642</v>
+        <v>1.7463</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.6857</v>
+        <v>-0.277</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.5451</v>
+        <v>0.0566</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.1406</v>
+        <v>-0.3336</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.6597</v>
+        <v>3.3418</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.6597</v>
+        <v>5.7895</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-2.4477</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.2725</v>
+        <v>2.2904</v>
       </c>
       <c r="E6" t="n">
-        <v>2.7269</v>
+        <v>2.5267</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.4544</v>
+        <v>-0.2364</v>
       </c>
       <c r="G6" t="n">
         <v>2.979</v>
@@ -922,13 +922,13 @@
         <v>1.5523</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.8125</v>
+        <v>-0.7946</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.0471</v>
+        <v>-0.2473</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.7653</v>
+        <v>-0.5473</v>
       </c>
       <c r="V6" t="n">
         <v>-0.2821</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.864</v>
+        <v>1.0097</v>
       </c>
       <c r="E7" t="n">
-        <v>0.9431</v>
+        <v>1.1433</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.0791</v>
+        <v>-0.1336</v>
       </c>
       <c r="G7" t="n">
         <v>2.7832</v>
@@ -1000,13 +1000,13 @@
         <v>1.1642</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.6072</v>
+        <v>-0.4615</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.5328000000000001</v>
+        <v>-0.3326</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.07439999999999999</v>
+        <v>-0.129</v>
       </c>
       <c r="V7" t="n">
         <v>-1.506</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.021</v>
+        <v>0.2487</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.2037</v>
+        <v>-0.043</v>
       </c>
       <c r="F9" t="n">
-        <v>0.1827</v>
+        <v>0.2917</v>
       </c>
       <c r="G9" t="n">
         <v>-0.0331</v>
@@ -1156,13 +1156,13 @@
         <v>0.194</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.1819</v>
+        <v>0.0878</v>
       </c>
       <c r="T9" t="n">
-        <v>0.0123</v>
+        <v>0.173</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.1943</v>
+        <v>-0.0852</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A. VIDAL RODRIGUEZ</t>
+          <t>A. MARTIN GONZALEZ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.0561</v>
+        <v>-1.1732</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.0484</v>
+        <v>-0.0156</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.0078</v>
+        <v>-1.1575</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.2937</v>
+        <v>1.341</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.6362</v>
+        <v>0.7382</v>
       </c>
       <c r="I10" t="n">
-        <v>0.3426</v>
+        <v>0.6028</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.2535</v>
+        <v>0.6469</v>
       </c>
       <c r="K10" t="n">
-        <v>-1.3347</v>
+        <v>0.7003</v>
       </c>
       <c r="L10" t="n">
-        <v>0.08119999999999999</v>
+        <v>-0.0533</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.0402</v>
+        <v>0.6941000000000001</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.3015</v>
+        <v>0.0379</v>
       </c>
       <c r="O10" t="n">
-        <v>0.2614</v>
+        <v>0.6562</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>-0.194</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.194</v>
+        <v>-0.9702</v>
       </c>
       <c r="R10" t="n">
-        <v>0.194</v>
+        <v>0.7761</v>
       </c>
       <c r="S10" t="n">
-        <v>0.8495</v>
+        <v>0.1276</v>
       </c>
       <c r="T10" t="n">
-        <v>1.1171</v>
+        <v>0.3076</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.2676</v>
+        <v>-0.18</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.6119</v>
+        <v>-2.4477</v>
       </c>
       <c r="W10" t="n">
-        <v>0.2821</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.894</v>
+        <v>-2.4477</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A. MARTIN GONZALEZ</t>
+          <t>P. SÁNCHEZ GUTIERREZ</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.4641</v>
+        <v>-1.4281</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.1157</v>
+        <v>-1.0518</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.3483</v>
+        <v>-0.3763</v>
       </c>
       <c r="G11" t="n">
-        <v>1.341</v>
+        <v>-0.318</v>
       </c>
       <c r="H11" t="n">
-        <v>0.7382</v>
+        <v>-1.2284</v>
       </c>
       <c r="I11" t="n">
-        <v>0.6028</v>
+        <v>0.9104</v>
       </c>
       <c r="J11" t="n">
-        <v>0.6469</v>
+        <v>0.0902</v>
       </c>
       <c r="K11" t="n">
-        <v>0.7003</v>
+        <v>-0.5643</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.0533</v>
+        <v>0.6546</v>
       </c>
       <c r="M11" t="n">
-        <v>0.6941000000000001</v>
+        <v>-0.4083</v>
       </c>
       <c r="N11" t="n">
-        <v>0.0379</v>
+        <v>-0.6641</v>
       </c>
       <c r="O11" t="n">
-        <v>0.6562</v>
+        <v>0.2558</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.194</v>
+        <v>-0.5821</v>
       </c>
       <c r="Q11" t="n">
-        <v>-0.9702</v>
+        <v>-1.1642</v>
       </c>
       <c r="R11" t="n">
-        <v>0.7761</v>
+        <v>0.5821</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.1633</v>
+        <v>-0.528</v>
       </c>
       <c r="T11" t="n">
-        <v>0.2075</v>
+        <v>0.0221</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.3708</v>
+        <v>-0.5501</v>
       </c>
       <c r="V11" t="n">
-        <v>-2.4477</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-2.4477</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A. REDONDO ALVAREZ DE SOTOMAYOR</t>
+          <t>A. VIDAL RODRIGUEZ</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,73 +1345,73 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.6922</v>
+        <v>-1.7418</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.3831</v>
+        <v>-0.7886</v>
       </c>
       <c r="F12" t="n">
-        <v>0.6909</v>
+        <v>-0.9533</v>
       </c>
       <c r="G12" t="n">
-        <v>0.6924</v>
+        <v>-1.2937</v>
       </c>
       <c r="H12" t="n">
-        <v>0.1524</v>
+        <v>-1.6362</v>
       </c>
       <c r="I12" t="n">
-        <v>0.54</v>
+        <v>0.3426</v>
       </c>
       <c r="J12" t="n">
-        <v>0.0823</v>
+        <v>-1.2535</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.2018</v>
+        <v>-1.3347</v>
       </c>
       <c r="L12" t="n">
-        <v>0.2842</v>
+        <v>0.08119999999999999</v>
       </c>
       <c r="M12" t="n">
-        <v>0.61</v>
+        <v>-0.0402</v>
       </c>
       <c r="N12" t="n">
-        <v>0.3542</v>
+        <v>-0.3015</v>
       </c>
       <c r="O12" t="n">
-        <v>0.2558</v>
+        <v>0.2614</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.5821</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>-1.9403</v>
+        <v>-0.194</v>
       </c>
       <c r="R12" t="n">
-        <v>1.3582</v>
+        <v>0.194</v>
       </c>
       <c r="S12" t="n">
-        <v>0.3632</v>
+        <v>0.1637</v>
       </c>
       <c r="T12" t="n">
-        <v>0.1346</v>
+        <v>0.3768</v>
       </c>
       <c r="U12" t="n">
-        <v>0.2286</v>
+        <v>-0.2131</v>
       </c>
       <c r="V12" t="n">
-        <v>-2.1657</v>
+        <v>-0.6119</v>
       </c>
       <c r="W12" t="n">
-        <v>-0.6597</v>
+        <v>0.2821</v>
       </c>
       <c r="X12" t="n">
-        <v>-1.506</v>
+        <v>-0.894</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>P. SÁNCHEZ GUTIERREZ</t>
+          <t>A. REDONDO ALVAREZ DE SOTOMAYOR</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,37 +1423,37 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-1.9252</v>
+        <v>-1.9558</v>
       </c>
       <c r="E13" t="n">
-        <v>-1.4127</v>
+        <v>-2.4832</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.5125999999999999</v>
+        <v>0.5274</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.318</v>
+        <v>0.6924</v>
       </c>
       <c r="H13" t="n">
-        <v>-1.2284</v>
+        <v>0.1524</v>
       </c>
       <c r="I13" t="n">
-        <v>0.9104</v>
+        <v>0.54</v>
       </c>
       <c r="J13" t="n">
-        <v>0.0902</v>
+        <v>0.0823</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.5643</v>
+        <v>-0.2018</v>
       </c>
       <c r="L13" t="n">
-        <v>0.6546</v>
+        <v>0.2842</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.4083</v>
+        <v>0.61</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.6641</v>
+        <v>0.3542</v>
       </c>
       <c r="O13" t="n">
         <v>0.2558</v>
@@ -1462,28 +1462,28 @@
         <v>-0.5821</v>
       </c>
       <c r="Q13" t="n">
-        <v>-1.1642</v>
+        <v>-1.9403</v>
       </c>
       <c r="R13" t="n">
-        <v>0.5821</v>
+        <v>1.3582</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.0251</v>
+        <v>0.09950000000000001</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.3387</v>
+        <v>0.0345</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.6864</v>
+        <v>0.06510000000000001</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>-2.1657</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>-0.6597</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>-1.506</v>
       </c>
     </row>
     <row r="14">
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>11.3709</v>
+        <v>11.6738</v>
       </c>
       <c r="E14" t="n">
-        <v>7.135899999999999</v>
+        <v>7.438800000000001</v>
       </c>
       <c r="F14" t="n">
-        <v>4.2348</v>
+        <v>4.234800000000001</v>
       </c>
       <c r="G14" t="n">
         <v>23.1591</v>
@@ -1522,7 +1522,7 @@
         <v>17.3933</v>
       </c>
       <c r="K14" t="n">
-        <v>3.7404</v>
+        <v>3.740400000000001</v>
       </c>
       <c r="L14" t="n">
         <v>13.6531</v>
@@ -1531,7 +1531,7 @@
         <v>5.765500000000001</v>
       </c>
       <c r="N14" t="n">
-        <v>0.5106000000000001</v>
+        <v>0.5106000000000002</v>
       </c>
       <c r="O14" t="n">
         <v>5.2551</v>
@@ -1546,10 +1546,10 @@
         <v>10.6718</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.8224</v>
+        <v>-1.5197</v>
       </c>
       <c r="T14" t="n">
-        <v>0.07269999999999993</v>
+        <v>0.3755000000000001</v>
       </c>
       <c r="U14" t="n">
         <v>-1.8952</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.7815</v>
+        <v>2.9479</v>
       </c>
       <c r="E15" t="n">
-        <v>2.2524</v>
+        <v>1.852</v>
       </c>
       <c r="F15" t="n">
-        <v>0.5291</v>
+        <v>1.0958</v>
       </c>
       <c r="G15" t="n">
         <v>-2.5563</v>
@@ -1624,13 +1624,13 @@
         <v>1.9403</v>
       </c>
       <c r="S15" t="n">
-        <v>0.3468</v>
+        <v>0.5131</v>
       </c>
       <c r="T15" t="n">
-        <v>0.8512</v>
+        <v>0.4508</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.5044999999999999</v>
+        <v>0.0623</v>
       </c>
       <c r="V15" t="n">
         <v>4.991</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.6131</v>
+        <v>2.3884</v>
       </c>
       <c r="E16" t="n">
-        <v>3.725</v>
+        <v>3.1244</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.1119</v>
+        <v>-0.736</v>
       </c>
       <c r="G16" t="n">
         <v>1.9431</v>
@@ -1702,13 +1702,13 @@
         <v>1.9403</v>
       </c>
       <c r="S16" t="n">
-        <v>1.1774</v>
+        <v>0.9528</v>
       </c>
       <c r="T16" t="n">
-        <v>1.2752</v>
+        <v>0.6746</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.0978</v>
+        <v>0.2782</v>
       </c>
       <c r="V16" t="n">
         <v>-2.4477</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>2.4657</v>
+        <v>2.148</v>
       </c>
       <c r="E17" t="n">
-        <v>2.1378</v>
+        <v>1.9376</v>
       </c>
       <c r="F17" t="n">
-        <v>0.3279</v>
+        <v>0.2104</v>
       </c>
       <c r="G17" t="n">
         <v>-2.3172</v>
@@ -1780,13 +1780,13 @@
         <v>3.2985</v>
       </c>
       <c r="S17" t="n">
-        <v>1.2306</v>
+        <v>0.913</v>
       </c>
       <c r="T17" t="n">
-        <v>0.7301</v>
+        <v>0.5299</v>
       </c>
       <c r="U17" t="n">
-        <v>0.5004999999999999</v>
+        <v>0.3831</v>
       </c>
       <c r="V17" t="n">
         <v>1.2239</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.4322</v>
+        <v>0.3711</v>
       </c>
       <c r="E18" t="n">
-        <v>1.7741</v>
+        <v>1.1735</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.3419</v>
+        <v>-0.8025</v>
       </c>
       <c r="G18" t="n">
         <v>-2.1501</v>
@@ -1858,13 +1858,13 @@
         <v>1.7463</v>
       </c>
       <c r="S18" t="n">
-        <v>0.3286</v>
+        <v>0.2675</v>
       </c>
       <c r="T18" t="n">
-        <v>0.8512</v>
+        <v>0.2506</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.5226</v>
+        <v>0.0168</v>
       </c>
       <c r="V18" t="n">
         <v>2.4477</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.1446</v>
+        <v>-0.2046</v>
       </c>
       <c r="E19" t="n">
-        <v>0.8342000000000001</v>
+        <v>0.1335</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.6896</v>
+        <v>-0.3381</v>
       </c>
       <c r="G19" t="n">
         <v>-1.2986</v>
@@ -1936,13 +1936,13 @@
         <v>0.9702</v>
       </c>
       <c r="S19" t="n">
-        <v>0.2194</v>
+        <v>-0.1298</v>
       </c>
       <c r="T19" t="n">
-        <v>0.6079</v>
+        <v>-0.09279999999999999</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.3885</v>
+        <v>-0.037</v>
       </c>
       <c r="V19" t="n">
         <v>1.2239</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-3.5158</v>
+        <v>-2.8179</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.1974</v>
+        <v>-1.4967</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.3184</v>
+        <v>-1.3212</v>
       </c>
       <c r="G20" t="n">
         <v>-5.5461</v>
@@ -2014,13 +2014,13 @@
         <v>1.3582</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.5518</v>
+        <v>0.1461</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.9691</v>
+        <v>-0.2684</v>
       </c>
       <c r="U20" t="n">
-        <v>0.4172</v>
+        <v>0.4144</v>
       </c>
       <c r="V20" t="n">
         <v>1.2239</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-4.1755</v>
+        <v>-3.5322</v>
       </c>
       <c r="E21" t="n">
-        <v>-3.6543</v>
+        <v>-2.9537</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.5212</v>
+        <v>-0.5785</v>
       </c>
       <c r="G21" t="n">
         <v>-3.4003</v>
@@ -2092,13 +2092,13 @@
         <v>1.7463</v>
       </c>
       <c r="S21" t="n">
-        <v>0.2844</v>
+        <v>0.9278</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.3017</v>
+        <v>0.399</v>
       </c>
       <c r="U21" t="n">
-        <v>0.5862000000000001</v>
+        <v>0.5289</v>
       </c>
       <c r="V21" t="n">
         <v>-1.8358</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-5.1812</v>
+        <v>-4.5561</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.2355</v>
+        <v>-2.6349</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.9456</v>
+        <v>-1.9212</v>
       </c>
       <c r="G22" t="n">
         <v>-3.4567</v>
@@ -2170,13 +2170,13 @@
         <v>1.7463</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.0244</v>
+        <v>0.6006</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.12</v>
+        <v>0.4806</v>
       </c>
       <c r="U22" t="n">
-        <v>0.0956</v>
+        <v>0.12</v>
       </c>
       <c r="V22" t="n">
         <v>-1.506</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-6.9354</v>
+        <v>-6.1135</v>
       </c>
       <c r="E23" t="n">
-        <v>-5.8712</v>
+        <v>-5.3707</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.0642</v>
+        <v>-0.7428</v>
       </c>
       <c r="G23" t="n">
         <v>-4.3769</v>
@@ -2248,13 +2248,13 @@
         <v>1.7463</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.1884</v>
+        <v>-0.3665</v>
       </c>
       <c r="T23" t="n">
-        <v>-1.0296</v>
+        <v>-0.5291</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.1588</v>
+        <v>0.1626</v>
       </c>
       <c r="V23" t="n">
         <v>-1.1761</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-11.3708</v>
+        <v>-9.368900000000002</v>
       </c>
       <c r="E24" t="n">
-        <v>-4.2349</v>
+        <v>-4.234999999999999</v>
       </c>
       <c r="F24" t="n">
-        <v>-7.1358</v>
+        <v>-5.134099999999999</v>
       </c>
       <c r="G24" t="n">
         <v>-23.1591</v>
@@ -2326,13 +2326,13 @@
         <v>16.4927</v>
       </c>
       <c r="S24" t="n">
-        <v>1.8226</v>
+        <v>3.8246</v>
       </c>
       <c r="T24" t="n">
         <v>1.8952</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.07269999999999982</v>
+        <v>1.9293</v>
       </c>
       <c r="V24" t="n">
         <v>4.1448</v>
